--- a/reports/pdf_change_20261028.xlsx
+++ b/reports/pdf_change_20261028.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,14 +553,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 10/10  ·  전일분: RISE, TIGER 기술이전, TIGER 코스닥, MIDAS  ·  전부 반영 완료</t>
+          <t>캡처 10/10  ·  전부 반영 완료</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,121억   ·   현금 -6억(-0.1%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 1종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,313억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -656,7 +656,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1359913692</v>
+        <v>1359914157</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,996억   ·   현금 62억(2.1%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,932억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -701,7 +701,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,019억   ·   현금 40억(1.9%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 6종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,112억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -797,7 +797,7 @@
         <v>300</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>4716746580</v>
+        <v>4723873290</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-150</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>-3654237350</v>
+        <v>-3659758675</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>45</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1115634691</v>
+        <v>1117320346</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-128</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>-5279048972</v>
+        <v>-5287025286</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2399086260</v>
+        <v>2402711130</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-49</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>-2614500904</v>
+        <v>-2618451252</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>28</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1069526425</v>
+        <v>1071142412</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-40</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>-4480412751</v>
+        <v>-4487182376</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>3323237590</v>
+        <v>3328258795</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2169703427</v>
+        <v>2172981713</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,079억   ·   현금 2억(0.1%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 4종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,032억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 4종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1118,7 +1118,7 @@
         <v>141</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>2113365342</v>
+        <v>2113363982</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>-228</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>-3606186407</v>
+        <v>-3606184086</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>86</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>807798360</v>
+        <v>807797840</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>33</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>652601691</v>
+        <v>652601271</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>18</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>584669060</v>
+        <v>584668684</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 233억   ·   현금 2억(0.9%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 241억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1263,7 +1263,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 414억   ·   현금 -2억(-0.4%)      ※전일분  PDF 2026-10-27  vs  2026-10-26      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 409억   ·   현금 -2억(-0.4%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1287,7 +1287,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,035억   ·   현금 69억(6.6%)      ※전일분  PDF 2026-10-27  vs  2026-10-26      매수 0종목  /  매도 1종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,014억   ·   현금 69억(6.9%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1302,282 +1302,277 @@
       <c r="K35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 855억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 292억   ·   현금 3억(1.1%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 5종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="14" t="n"/>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I38" s="17" t="n">
-        <v>-507847568</v>
-      </c>
-      <c r="J38" s="18" t="inlineStr">
-        <is>
-          <t>2.08%→1.58%</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>12→9</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 799억   ·   현금 2억(0.2%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 281억   ·   현금 2억(0.7%)      ※전일분  PDF 2026-10-27  vs  2026-10-26      매수 3종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-    </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>267208890</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>2.05%→3.12%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>26→37</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>-247232426</v>
+      </c>
+      <c r="J44" s="18" t="inlineStr">
+        <is>
+          <t>2.97%→2.02%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>272→191</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K45" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>한양디지텍</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>78832306</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>4.04%→4.81%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>83→88</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>HLB이노베이션  (편출)</t>
+        </is>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>-181425869</v>
+      </c>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>0.66%→0.00%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>29→0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>루닛  (신규)</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>380838519</v>
+        <v>187934534</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.36%</t>
+          <t>0.44%→1.14%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>0→61</t>
+          <t>3→7</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="H46" s="17" t="n">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="I46" s="17" t="n">
-        <v>-103279323</v>
+        <v>-66686448</v>
       </c>
       <c r="J46" s="18" t="inlineStr">
         <is>
-          <t>2.57%→1.93%</t>
+          <t>1.10%→0.88%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>118→99</t>
+          <t>77→61</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>에이팩트</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>151325607</v>
+        <v>148023705</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>2.38%→3.08%</t>
+          <t>5.55%→6.33%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>178→216</t>
+          <t>34→37</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
@@ -1586,118 +1581,173 @@
         </is>
       </c>
       <c r="H47" s="17" t="n">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="I47" s="17" t="n">
-        <v>-199856391</v>
+        <v>-138930099</v>
       </c>
       <c r="J47" s="18" t="inlineStr">
         <is>
-          <t>4.29%→3.58%</t>
+          <t>3.58%→2.80%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>90→75</t>
+          <t>75→64</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>198050140</v>
+        <v>43889281</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>1.19%→2.06%</t>
+          <t>0.94%→1.01%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>19→29</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H48" s="17" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="I48" s="17" t="n">
-        <v>-107546326</v>
+        <v>-98892970</v>
       </c>
       <c r="J48" s="18" t="inlineStr">
         <is>
-          <t>0.93%→0.49%</t>
+          <t>1.99%→1.31%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>16→9</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 53억   ·   현금 1억(1.8%)      ※전일분  PDF 2026-10-27  vs  2026-10-26      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+          <t>29→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="n"/>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>-113670081</v>
+      </c>
+      <c r="J49" s="18" t="inlineStr">
+        <is>
+          <t>3.34%→2.76%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>32→28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="n"/>
+      <c r="B50" s="14" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="14" t="n"/>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>-152570509</v>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
+        <is>
+          <t>3.65%→2.78%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>25→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 55억   ·   현금 1억(1.7%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="26">
     <mergeCell ref="G12:K12"/>
     <mergeCell ref="A30:K30"/>
-    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A41:K41"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A50:K50"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A42:E42"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>
     <mergeCell ref="A32:K32"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="G44:K44"/>
-    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A52:K52"/>
     <mergeCell ref="G22:K22"/>
-    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20261028.xlsx
+++ b/reports/pdf_change_20261028.xlsx
@@ -1263,7 +1263,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 409억   ·   현금 -2억(-0.4%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 409억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1287,7 +1287,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,014억   ·   현금 69억(6.9%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,014억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1335,7 +1335,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 292억   ·   현금 3억(1.1%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 5종목  /  매도 7종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 292억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 5종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -1556,23 +1556,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>148023705</v>
+        <v>43889281</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>5.55%→6.33%</t>
+          <t>0.94%→1.01%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>34→37</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
@@ -1600,23 +1600,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>43889281</v>
+        <v>148023705</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.01%</t>
+          <t>5.55%→6.33%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>34→37</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 55억   ·   현금 1억(1.7%)      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 55억      당일 2026-10-28  vs  전영업일 2026-10-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>

--- a/reports/pdf_change_20261028.xlsx
+++ b/reports/pdf_change_20261028.xlsx
@@ -1556,23 +1556,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>43889281</v>
+        <v>148023705</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.01%</t>
+          <t>5.55%→6.33%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>34→37</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
@@ -1600,23 +1600,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>148023705</v>
+        <v>43889281</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>5.55%→6.33%</t>
+          <t>0.94%→1.01%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>34→37</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">

--- a/reports/pdf_change_20261028.xlsx
+++ b/reports/pdf_change_20261028.xlsx
@@ -1556,23 +1556,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>148023705</v>
+        <v>43889281</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>5.55%→6.33%</t>
+          <t>0.94%→1.01%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>34→37</t>
+          <t>17→20</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
@@ -1600,23 +1600,23 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>43889281</v>
+        <v>148023705</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.94%→1.01%</t>
+          <t>5.55%→6.33%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>17→20</t>
+          <t>34→37</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
